--- a/datos_de_prueba/02_caso_con_problemas/PL-03_toma_inventario_fisico.xlsx
+++ b/datos_de_prueba/02_caso_con_problemas/PL-03_toma_inventario_fisico.xlsx
@@ -455,13 +455,13 @@
     <t>166002092</t>
   </si>
   <si>
-    <t>EQUIPO CONTADO DESPUES DEL CORTE</t>
+    <t>EQUIPO CON TOMA EN EL FUTURO</t>
   </si>
   <si>
     <t>SN-X9</t>
   </si>
   <si>
-    <t>2026-02-14</t>
+    <t>2030-02-14</t>
   </si>
 </sst>
 </file>
